--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -9662,38 +9662,30 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>9047000</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>23257</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K136" s="5" t="n">
+        <v>9047000</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>23257</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9702,7 +9694,7 @@
       </c>
       <c r="N136" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10624,38 +10616,30 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>8826000</v>
+      </c>
+      <c r="I151" s="5" t="n">
+        <v>22689</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K151" s="5" t="n">
+        <v>8826000</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>22689</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10664,7 +10648,7 @@
       </c>
       <c r="N151" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -17800,7 +17784,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -17816,7 +17800,7 @@
         <v>7185000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>18662</v>
+        <v>18711</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -17827,7 +17811,7 @@
         <v>7185000</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>18662</v>
+        <v>18711</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -47470,7 +47454,7 @@
         </is>
       </c>
       <c r="E730" s="4" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F730" s="3" t="inlineStr">
         <is>
@@ -47486,7 +47470,7 @@
         <v>6398000</v>
       </c>
       <c r="I730" s="5" t="n">
-        <v>16618</v>
+        <v>16661</v>
       </c>
       <c r="J730" s="3" t="inlineStr">
         <is>
@@ -47497,7 +47481,7 @@
         <v>6398000</v>
       </c>
       <c r="L730" s="5" t="n">
-        <v>16618</v>
+        <v>16661</v>
       </c>
       <c r="M730" s="3" t="inlineStr">
         <is>
@@ -48981,7 +48965,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48991,7 +48975,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>222</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50117,12 +50101,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
+$905万
+$23,257/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -50244,12 +50228,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 389呎 (2房)
-招标单位
--
-(在售)</t>
+$883万
+$22,689/呎
+(26年-09月-05日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -51310,9 +51294,9 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>H | 385呎 (2房)
+          <t>H | 384呎 (2房)
 $718万
-$18,662/呎
+$18,711/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -55436,9 +55420,9 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>H | 385呎 (2房)
+          <t>H | 384呎 (2房)
 $640万
-$16,618/呎
+$16,661/呎
 (25年-10月-16日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -11280,7 +11280,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -11296,7 +11296,7 @@
         <v>8886000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>22668</v>
+        <v>22611</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>8886000</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>22668</v>
+        <v>22611</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -50397,9 +50397,9 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>G | 392呎 (2房)
+          <t>G | 393呎 (2房)
 $889万
-$22,668/呎
+$22,611/呎
 (26年-07月-16日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8247,7 +8247,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -31654,7 +31654,7 @@
         </is>
       </c>
       <c r="E478" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
@@ -31663,14 +31663,14 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
         <v>9505000</v>
       </c>
       <c r="I478" s="5" t="n">
-        <v>24817</v>
+        <v>24882</v>
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
@@ -31681,7 +31681,7 @@
         <v>9505000</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>24817</v>
+        <v>24882</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -46694,7 +46694,7 @@
         </is>
       </c>
       <c r="E718" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
@@ -46710,7 +46710,7 @@
         <v>8106000</v>
       </c>
       <c r="I718" s="5" t="n">
-        <v>21164</v>
+        <v>21220</v>
       </c>
       <c r="J718" s="3" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>8106000</v>
       </c>
       <c r="L718" s="5" t="n">
-        <v>21164</v>
+        <v>21220</v>
       </c>
       <c r="M718" s="3" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         </is>
       </c>
       <c r="E733" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         <v>6222000</v>
       </c>
       <c r="I733" s="5" t="n">
-        <v>16245</v>
+        <v>16288</v>
       </c>
       <c r="J733" s="3" t="inlineStr">
         <is>
@@ -47667,7 +47667,7 @@
         <v>6222000</v>
       </c>
       <c r="L733" s="5" t="n">
-        <v>16245</v>
+        <v>16288</v>
       </c>
       <c r="M733" s="3" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
           <t>J | 287呎 (1房)
 $704万
 $24,533/呎
-(26年-08月-28日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -53237,10 +53237,10 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $950万
-$24,817/呎
-(26年-08月-24日)</t>
+$24,882/呎
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="G11" s="23" t="inlineStr">
@@ -53407,7 +53407,7 @@
           <t>K | 393呎 (2房)
 $933万
 $23,748/呎
-(26年-08月-29日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -55269,9 +55269,9 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $811万
-$21,164/呎
+$21,220/呎
 (26年-07月-29日)</t>
         </is>
       </c>
@@ -55396,9 +55396,9 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $622万
-$16,245/呎
+$16,288/呎
 (24年-10月-23日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -40430,7 +40430,7 @@
         </is>
       </c>
       <c r="E618" s="4" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F618" s="3" t="inlineStr">
         <is>
@@ -40439,14 +40439,14 @@
       </c>
       <c r="G618" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H618" s="5" t="n">
         <v>9428000</v>
       </c>
       <c r="I618" s="5" t="n">
-        <v>21282</v>
+        <v>21330</v>
       </c>
       <c r="J618" s="3" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>9428000</v>
       </c>
       <c r="L618" s="5" t="n">
-        <v>21282</v>
+        <v>21330</v>
       </c>
       <c r="M618" s="3" t="inlineStr">
         <is>
@@ -54587,10 +54587,10 @@
       </c>
       <c r="P21" s="23" t="inlineStr">
         <is>
-          <t>Q | 443呎 (2房)
+          <t>Q | 442呎 (2房)
 $943万
-$21,282/呎
-(26年-08月-24日)</t>
+$21,330/呎
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -7463,7 +7463,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -49884,7 +49884,7 @@
           <t>F | 262呎 (1房)
 $650万
 $24,790/呎
-(26年-09月-03日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -50106,7 +50106,7 @@
           <t>B | 389呎 (2房)
 $905万
 $23,257/呎
-(26年-09月-05日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -50233,7 +50233,7 @@
           <t>B | 389呎 (2房)
 $883万
 $22,689/呎
-(26年-09月-05日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -9980,34 +9980,34 @@
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
-        <v>8454000</v>
+        <v>10587000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>21403</v>
+        <v>26803</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>8454000</v>
+        <v>8681340</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>21403</v>
+        <v>21978</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N141" s="3" t="inlineStr">
@@ -34083,7 +34083,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -48970,12 +48970,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>221</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50308,12 +50308,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="M14" s="23" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>M | 395呎 (2房)
-$845万
-$21,403/呎
-(26年-09月-01日)</t>
+$1059万
+$26,803/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -53677,7 +53677,7 @@
           <t>M | 397呎 (2房)
 $845万
 $21,295/呎
-(26年-08月-06日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="N14" s="23" t="inlineStr">

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -35268,7 +35268,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>8706000</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>22613</v>
+        <v>22672</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>8706000</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>22613</v>
+        <v>22672</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -53769,9 +53769,9 @@
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>H | 385呎 (2房)
+          <t>H | 384呎 (2房)
 $871万
-$22,613/呎
+$22,672/呎
 (26年-07月-17日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -8436,34 +8436,34 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>7729000</v>
+        <v>6337000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>29500</v>
+        <v>24187</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="5" t="n">
-        <v>6337780</v>
+        <v>6337000</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>24190</v>
+        <v>24187</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>120天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>9243000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>23579</v>
+        <v>23519</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>9243000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>23579</v>
+        <v>23519</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>8986000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>23462</v>
+        <v>23524</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>8986000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>23462</v>
+        <v>23524</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -11082,38 +11082,30 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>8808000</v>
+      </c>
+      <c r="I158" s="5" t="n">
+        <v>22819</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K158" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K158" s="5" t="n">
+        <v>8808000</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>22819</v>
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
@@ -11122,7 +11114,7 @@
       </c>
       <c r="N158" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23842,38 +23834,30 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H362" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I362" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="H362" s="5" t="n">
+        <v>9298000</v>
+      </c>
+      <c r="I362" s="5" t="n">
+        <v>20801</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K362" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L362" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K362" s="5" t="n">
+        <v>9298000</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>20801</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -23882,7 +23866,7 @@
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -31530,7 +31514,7 @@
         </is>
       </c>
       <c r="E476" s="4" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
@@ -31546,7 +31530,7 @@
         <v>9639000</v>
       </c>
       <c r="I476" s="5" t="n">
-        <v>24589</v>
+        <v>24527</v>
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
@@ -31557,7 +31541,7 @@
         <v>9639000</v>
       </c>
       <c r="L476" s="5" t="n">
-        <v>24589</v>
+        <v>24527</v>
       </c>
       <c r="M476" s="3" t="inlineStr">
         <is>
@@ -48965,7 +48949,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -48975,7 +48959,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -50006,12 +49990,12 @@
 (26年-07月-27日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 262呎 (1房)
-$773万
-$29,500/呎
-(在售)</t>
+$634万
+$24,187/呎
+(26年-10月-22日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -50127,9 +50111,9 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>E | 383呎 (2房)
+          <t>E | 382呎 (2房)
 $899万
-$23,462/呎
+$23,524/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -50143,9 +50127,9 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>G | 392呎 (2房)
+          <t>G | 393呎 (2房)
 $924万
-$23,579/呎
+$23,519/呎
 (26年-07月-28日)</t>
         </is>
       </c>
@@ -50419,12 +50403,12 @@
 (26年-07月-30日)</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="23" t="inlineStr">
         <is>
           <t>K | 386呎 (2房)
-招标单位
--
-(在售)</t>
+$881万
+$22,819/呎
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -51998,12 +51982,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 447呎 (2房)
-招标单位
--
-(在售)</t>
+$930万
+$20,801/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -53253,9 +53237,9 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>G | 392呎 (2房)
+          <t>G | 393呎 (2房)
 $964万
-$24,589/呎
+$24,527/呎
 (26年-08月-12日)</t>
         </is>
       </c>

--- a/files/九龙-启德-柏蔚森 II.xlsx
+++ b/files/九龙-启德-柏蔚森 II.xlsx
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>9243000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>23519</v>
+        <v>23579</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>9243000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>23519</v>
+        <v>23579</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>8986000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>23524</v>
+        <v>23462</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>8986000</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>23524</v>
+        <v>23462</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         <v>9018000</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>22947</v>
+        <v>23005</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>9018000</v>
       </c>
       <c r="L146" s="5" t="n">
-        <v>22947</v>
+        <v>23005</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
@@ -11288,7 +11288,7 @@
         <v>8886000</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>22611</v>
+        <v>22668</v>
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>8886000</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>22611</v>
+        <v>22668</v>
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>7185000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>18711</v>
+        <v>18662</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>7185000</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>18711</v>
+        <v>18662</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -31514,7 +31514,7 @@
         </is>
       </c>
       <c r="E476" s="4" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F476" s="3" t="inlineStr">
         <is>
@@ -31530,7 +31530,7 @@
         <v>9639000</v>
       </c>
       <c r="I476" s="5" t="n">
-        <v>24527</v>
+        <v>24589</v>
       </c>
       <c r="J476" s="3" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>9639000</v>
       </c>
       <c r="L476" s="5" t="n">
-        <v>24527</v>
+        <v>24589</v>
       </c>
       <c r="M476" s="3" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         </is>
       </c>
       <c r="E478" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F478" s="3" t="inlineStr">
         <is>
@@ -31654,7 +31654,7 @@
         <v>9505000</v>
       </c>
       <c r="I478" s="5" t="n">
-        <v>24882</v>
+        <v>24817</v>
       </c>
       <c r="J478" s="3" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>9505000</v>
       </c>
       <c r="L478" s="5" t="n">
-        <v>24882</v>
+        <v>24817</v>
       </c>
       <c r="M478" s="3" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>9624000</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>21774</v>
+        <v>21725</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>9624000</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>21774</v>
+        <v>21725</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>8706000</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>22672</v>
+        <v>22613</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>8706000</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>22672</v>
+        <v>22613</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="E618" s="4" t="n">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F618" s="3" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>9428000</v>
       </c>
       <c r="I618" s="5" t="n">
-        <v>21330</v>
+        <v>21282</v>
       </c>
       <c r="J618" s="3" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>9428000</v>
       </c>
       <c r="L618" s="5" t="n">
-        <v>21330</v>
+        <v>21282</v>
       </c>
       <c r="M618" s="3" t="inlineStr">
         <is>
@@ -46678,7 +46678,7 @@
         </is>
       </c>
       <c r="E718" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F718" s="3" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>8106000</v>
       </c>
       <c r="I718" s="5" t="n">
-        <v>21220</v>
+        <v>21164</v>
       </c>
       <c r="J718" s="3" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>8106000</v>
       </c>
       <c r="L718" s="5" t="n">
-        <v>21220</v>
+        <v>21164</v>
       </c>
       <c r="M718" s="3" t="inlineStr">
         <is>
@@ -47438,7 +47438,7 @@
         </is>
       </c>
       <c r="E730" s="4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F730" s="3" t="inlineStr">
         <is>
@@ -47454,7 +47454,7 @@
         <v>6398000</v>
       </c>
       <c r="I730" s="5" t="n">
-        <v>16661</v>
+        <v>16618</v>
       </c>
       <c r="J730" s="3" t="inlineStr">
         <is>
@@ -47465,7 +47465,7 @@
         <v>6398000</v>
       </c>
       <c r="L730" s="5" t="n">
-        <v>16661</v>
+        <v>16618</v>
       </c>
       <c r="M730" s="3" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         </is>
       </c>
       <c r="E733" s="4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F733" s="3" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>6222000</v>
       </c>
       <c r="I733" s="5" t="n">
-        <v>16288</v>
+        <v>16245</v>
       </c>
       <c r="J733" s="3" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>6222000</v>
       </c>
       <c r="L733" s="5" t="n">
-        <v>16288</v>
+        <v>16245</v>
       </c>
       <c r="M733" s="3" t="inlineStr">
         <is>
@@ -50111,9 +50111,9 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $899万
-$23,524/呎
+$23,462/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -50127,9 +50127,9 @@
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>G | 393呎 (2房)
+          <t>G | 392呎 (2房)
 $924万
-$23,519/呎
+$23,579/呎
 (26年-07月-28日)</t>
         </is>
       </c>
@@ -50254,9 +50254,9 @@
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>G | 393呎 (2房)
+          <t>G | 392呎 (2房)
 $902万
-$22,947/呎
+$23,005/呎
 (26年-08月-25日)</t>
         </is>
       </c>
@@ -50381,9 +50381,9 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>G | 393呎 (2房)
+          <t>G | 392呎 (2房)
 $889万
-$22,611/呎
+$22,668/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -51278,9 +51278,9 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>H | 384呎 (2房)
+          <t>H | 385呎 (2房)
 $718万
-$18,711/呎
+$18,662/呎
 (25年-12月-09日)</t>
         </is>
       </c>
@@ -53221,9 +53221,9 @@
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $950万
-$24,882/呎
+$24,817/呎
 (26年-09月-17日)</t>
         </is>
       </c>
@@ -53237,9 +53237,9 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>G | 393呎 (2房)
+          <t>G | 392呎 (2房)
 $964万
-$24,527/呎
+$24,589/呎
 (26年-08月-12日)</t>
         </is>
       </c>
@@ -53682,9 +53682,9 @@
       </c>
       <c r="P14" s="23" t="inlineStr">
         <is>
-          <t>Q | 442呎 (2房)
+          <t>Q | 443呎 (2房)
 $962万
-$21,774/呎
+$21,725/呎
 (26年-07月-16日)</t>
         </is>
       </c>
@@ -53753,9 +53753,9 @@
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>H | 384呎 (2房)
+          <t>H | 385呎 (2房)
 $871万
-$22,672/呎
+$22,613/呎
 (26年-07月-17日)</t>
         </is>
       </c>
@@ -54571,9 +54571,9 @@
       </c>
       <c r="P21" s="23" t="inlineStr">
         <is>
-          <t>Q | 442呎 (2房)
+          <t>Q | 443呎 (2房)
 $943万
-$21,330/呎
+$21,282/呎
 (26年-09月-18日)</t>
         </is>
       </c>
@@ -55253,9 +55253,9 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $811万
-$21,220/呎
+$21,164/呎
 (26年-07月-29日)</t>
         </is>
       </c>
@@ -55380,9 +55380,9 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>E | 382呎 (2房)
+          <t>E | 383呎 (2房)
 $622万
-$16,288/呎
+$16,245/呎
 (24年-10月-23日)</t>
         </is>
       </c>
@@ -55404,9 +55404,9 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>H | 384呎 (2房)
+          <t>H | 385呎 (2房)
 $640万
-$16,661/呎
+$16,618/呎
 (25年-10月-16日)</t>
         </is>
       </c>
